--- a/product_selector_out/STM32MP151.xlsx
+++ b/product_selector_out/STM32MP151.xlsx
@@ -1461,7 +1461,7 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp151c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp151a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2815,9 +2815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -2970,14 +2970,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AJ13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AJ13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL13" s="6" t="inlineStr">
@@ -3065,9 +3065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3092,9 +3092,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3247,14 +3247,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AJ14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AJ14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL14" s="6" t="inlineStr">
@@ -3342,9 +3342,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3740,7 +3740,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32MP151F</t>
+          <t>STM32MP151A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32MP151F</t>
+          <t>STM32MP151A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3777,14 +3777,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32MP151F</t>
+          <t>STM32MP151A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3798,138 +3798,6 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32MP151D</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32MP151D</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32MP151D</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32MP151A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32MP151A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32MP151A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
         <is>
           <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32MP151.xlsx
+++ b/product_selector_out/STM32MP151.xlsx
@@ -1461,7 +1461,7 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp151c.pdf</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp151a.pdf</t>
         </is>
       </c>
     </row>
@@ -2815,9 +2815,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -2970,14 +2970,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AJ13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AJ13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL13" s="6" t="inlineStr">
@@ -3065,9 +3065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3092,9 +3092,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3247,14 +3247,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AJ14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AJ14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL14" s="6" t="inlineStr">
@@ -3342,9 +3342,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3740,7 +3740,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32MP151A</t>
+          <t>STM32MP151F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32MP151A</t>
+          <t>STM32MP151F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3777,27 +3777,159 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>STM32MP151F</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32MP151D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32MP151D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32MP151D</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>STM32MP151A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A7, Arm Cortex-M4; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32MP151A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32MP151A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32MP151.xlsx
+++ b/product_selector_out/STM32MP151.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC15"/>
+  <dimension ref="A1:BD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.828125" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,8 @@
     <col width="18" customWidth="1" min="52" max="52"/>
     <col width="18" customWidth="1" min="53" max="53"/>
     <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="52" customWidth="1" min="55" max="55"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="52" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -833,6 +834,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -910,6 +916,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1184,6 +1191,11 @@
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp151c.pdf</t>
         </is>
       </c>
@@ -1464,6 +1476,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1741,6 +1758,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2015,12 +2037,17 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp151a.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="56">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2033,16 +2060,18 @@
     <mergeCell ref="V10:V11"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="M10:M11"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AJ10:AJ11"/>
-    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AP10:AP11"/>
-    <mergeCell ref="BA10:BA11"/>
-    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="AK10:AK11"/>
@@ -2054,9 +2083,8 @@
     <mergeCell ref="Z10:Z11"/>
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
-    <mergeCell ref="A1:BC8"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A9:BC9"/>
+    <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="AE10:AF10"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
@@ -2094,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC15"/>
+  <dimension ref="A1:BD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2152,6 +2180,7 @@
     <col width="16" customWidth="1" min="53" max="53"/>
     <col width="16" customWidth="1" min="54" max="54"/>
     <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2439,6 +2468,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -2516,6 +2550,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2788,7 +2823,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="6" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3070,6 +3110,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3347,6 +3392,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3619,7 +3669,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="6" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3627,8 +3682,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BC9"/>
-    <mergeCell ref="A1:BC8"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
